--- a/artfynd/A 60596-2025 artfynd.xlsx
+++ b/artfynd/A 60596-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>123324351</v>
       </c>
       <c r="B2" t="n">
-        <v>91277</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -810,15 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123324352</v>
+        <v>123324349</v>
       </c>
       <c r="B3" t="n">
-        <v>90990</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -845,12 +835,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -859,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>603125</v>
+        <v>603190</v>
       </c>
       <c r="R3" t="n">
-        <v>6996906</v>
+        <v>6996974</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +879,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1261</t>
+          <t>2024_1264</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +889,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,12 +899,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:08</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>på granlåga vid bäck</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,7 +919,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -945,15 +930,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123324349</v>
+        <v>123324352</v>
       </c>
       <c r="B4" t="n">
-        <v>90990</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -980,12 +960,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -994,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>603190</v>
+        <v>603125</v>
       </c>
       <c r="R4" t="n">
-        <v>6996974</v>
+        <v>6996906</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,7 +1004,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1264</t>
+          <t>2024_1261</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1034,7 +1014,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1044,7 +1024,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:08</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>på granlåga vid bäck</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1064,7 +1049,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 60596-2025 artfynd.xlsx
+++ b/artfynd/A 60596-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -802,6 +807,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123324351</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -927,6 +937,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123324349</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1057,8 +1072,18 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123324352</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>